--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,31 @@
           <t>PnL_R$</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Fonte_Placar</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>PnL_stake_u</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Convencao_PnL</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Placar_Original</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado_Original</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -590,17 +615,15 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0.95</v>
       </c>
@@ -609,11 +632,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T2" t="n">
-        <v>5</v>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -676,17 +708,15 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>RED</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
         <v>-4.7</v>
       </c>
@@ -695,11 +725,20 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S3" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-100</v>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0x0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -762,17 +801,15 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>3x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0.95</v>
       </c>
@@ -781,11 +818,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T4" t="n">
-        <v>19.39</v>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3x0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -848,17 +894,15 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0x2</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>0.95</v>
       </c>
@@ -867,11 +911,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T5" t="n">
-        <v>13.97</v>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0x2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -934,17 +987,15 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>1x0</t>
+          <t>?</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
         <v>0.95</v>
       </c>
@@ -953,11 +1004,20 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="T6" t="n">
-        <v>5.28</v>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1x0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
@@ -615,15 +615,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
       <c r="Q2" t="n">
         <v>0.95</v>
       </c>
@@ -632,11 +634,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>1x0</t>
@@ -708,15 +724,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>0x0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
       <c r="Q3" t="n">
         <v>-4.7</v>
       </c>
@@ -725,11 +743,25 @@
           <t>RED</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>-4.7</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>0x0</t>
@@ -801,15 +833,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>3x0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
       <c r="Q4" t="n">
         <v>0.95</v>
       </c>
@@ -818,11 +852,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>0.19388</v>
+      </c>
+      <c r="T4" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>3x0</t>
@@ -894,15 +942,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>0x2</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
       <c r="Q5" t="n">
         <v>0.95</v>
       </c>
@@ -911,11 +961,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>0.13971</v>
+      </c>
+      <c r="T5" t="n">
+        <v>13.97</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>0x2</t>
@@ -987,15 +1051,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>1x0</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
       <c r="Q6" t="n">
         <v>0.95</v>
       </c>
@@ -1004,11 +1070,25 @@
           <t>GREEN</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>0.05278</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>LIABILITY=1u;comissao=5%</t>
+        </is>
+      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>1x0</t>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-09-07.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,31 +529,6 @@
           <t>PnL_R$</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Fonte_Placar</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>PnL_stake_u</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Convencao_PnL</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Placar_Original</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Resultado_Original</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -635,33 +610,10 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="T2" t="n">
         <v>5</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1x0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="3">
@@ -744,33 +696,10 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-1</v>
+        <v>-4.7</v>
       </c>
       <c r="T3" t="n">
         <v>-100</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0x0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>RED</t>
-        </is>
       </c>
     </row>
     <row r="4">
@@ -853,33 +782,10 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.19388</v>
+        <v>0.95</v>
       </c>
       <c r="T4" t="n">
         <v>19.39</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3x0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -962,33 +868,10 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>0.13971</v>
+        <v>0.95</v>
       </c>
       <c r="T5" t="n">
         <v>13.97</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0x2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -1071,33 +954,10 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0.05278</v>
+        <v>0.95</v>
       </c>
       <c r="T6" t="n">
         <v>5.28</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="V6" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>LIABILITY=1u;comissao=5%</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1x0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
       </c>
     </row>
   </sheetData>
